--- a/OMOP Analysis/Results/Output_visits_OMOP-Unadjusted_Boot.xlsx
+++ b/OMOP Analysis/Results/Output_visits_OMOP-Unadjusted_Boot.xlsx
@@ -377,10 +377,10 @@
         <v>23.669</v>
       </c>
       <c r="B2">
-        <v>23.363</v>
+        <v>23.351</v>
       </c>
       <c r="C2">
-        <v>23.987</v>
+        <v>23.977</v>
       </c>
     </row>
   </sheetData>
@@ -415,10 +415,10 @@
         <v>24.415</v>
       </c>
       <c r="B2">
-        <v>24.089</v>
+        <v>24.095</v>
       </c>
       <c r="C2">
-        <v>24.741</v>
+        <v>24.744</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_visits_OMOP-Unadjusted_Boot.xlsx
+++ b/OMOP Analysis/Results/Output_visits_OMOP-Unadjusted_Boot.xlsx
@@ -374,13 +374,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>23.669</v>
+        <v>21.398</v>
       </c>
       <c r="B2">
-        <v>23.351</v>
+        <v>21.037</v>
       </c>
       <c r="C2">
-        <v>23.977</v>
+        <v>21.762</v>
       </c>
     </row>
   </sheetData>
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>24.415</v>
+        <v>22.314</v>
       </c>
       <c r="B2">
-        <v>24.095</v>
+        <v>21.962</v>
       </c>
       <c r="C2">
-        <v>24.744</v>
+        <v>22.664</v>
       </c>
     </row>
   </sheetData>
